--- a/think3d_repro/outputs/run1/vlmeval_runs/SPAgent_4B_px256k_pi3x_spatial/VSIBench/SPAgent_4B_px256k_pi3x_spatial_VSIBench.xlsx
+++ b/think3d_repro/outputs/run1/vlmeval_runs/SPAgent_4B_px256k_pi3x_spatial/VSIBench/SPAgent_4B_px256k_pi3x_spatial_VSIBench.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="366">
   <si>
     <t>id</t>
   </si>
@@ -1874,7 +1874,34 @@
 &lt;answer&gt;(C) C. coat rack&lt;/answer&gt;</t>
   </si>
   <si>
-    <t>&lt;answer&gt;(D) D. plant&lt;/answer&gt;</t>
+    <t>To determine which of the objects (kettle, cutting board, refrigerator, plant) is closest to the sofa, we need to analyze the spatial relationships between these objects and the sofa across the provided frames. The frames show different parts of the house, including the living room with the sofa and the kitchen. We need to identify the positions of the objects in question relative to the sofa.
+Step 1: Identify the positions of the sofa and the objects in the frames.
+- The sofa is prominently visible in the frames, particularly in the third and fourth frames.
+- The kitchen area is shown in frames 5 and 6, where the kettle, cutting board, and refrigerator are located.
+- The plant is visible in frames 1 and 2, near the dining table.
+Step 2: Determine the relative positions of the objects to the sofa.
+- The kettle is in the kitchen, which is adjacent to the living room.
+- The cutting board is also in the kitchen, near the sink.
+- The refrigerator is in the kitchen, on the left side of the counter.
+- The plant is in the dining area, which is near the living room.
+Step 3: Estimate the distance from the sofa to each object.
+- The kettle, cutting board, and refrigerator are all in the kitchen, which is adjacent to the living room. The distance from the sofa to the kitchen is relatively short.
+- The plant is in the dining area, which is further from the living room than the kitchen.
+Step 4: Compare the distances to determine which object is closest to the sofa.
+- The kettle, cutting board, and refrigerator are all in the kitchen, which is adjacent to the living room. The plant is in the dining area, which is further from the living room than the kitchen.
+- Therefore, the kettle, cutting board, and refrigerator are all closer to the sofa than the plant.
+Step 5: Choose the closest object.
+- The kettle, cutting board, and refrigerator are all closer to the sofa than the plant. However, the question asks for the closest object, so we need to determine which of these three is closest to the sofa.
+- The kettle is on the countertop near the sink, which is closer to the sofa than the cutting board or refrigerator.
+- The cutting board is on the countertop near the sink, which is also closer to the sofa than the refrigerator.
+- The refrigerator is on the left side of the counter, which is further from the sofa than the kettle and cutting board.
+- Therefore, the kettle and cutting board are both closer to the sofa than the refrigerator.
+- The plant is in the dining area, which is further from the sofa than the kitchen.
+- Therefore, the kettle and cutting board are both closer to the sofa than the plant.
+- The question asks for the closest object, so we need to determine which of the kettle and cutting board is closest to the sofa.
+- The kettle is on the countertop near the sink, which is closer to the sofa than the cutting board.
+- Therefore, the kettle is the closest object to the sofa.
+&lt;answer&gt;(A) A. kettle&lt;/answer&gt;</t>
   </si>
   <si>
     <t>To determine which object (chair, bed, tv, table) is closest to the stove, we need to analyze the spatial relationships between these objects and the stove based on the provided images. The stove is visible in the fifth image, embedded in a kitchen countertop with wooden cabinets. The question asks for the closest object to the stove, so we must identify the positions of the chair, bed, tv, and table relative to the stove.
@@ -1948,6 +1975,25 @@
   <si>
     <t>The backpack is inferred to be on the kitchen island or counter, as a blue bag (likely the backpack) is visible on the counter in the first frame. The counter is in the foreground, close to the backpack. The clock is on the wall, the door is in the background, and the plant is on the counter near the sink. Comparing distances, the counter is closest to the backpack.
 &lt;answer&gt;B&lt;/answer&gt;</t>
+  </si>
+  <si>
+    <t>To determine which object (window, table, door, chair) is closest to the trash bin, we need to analyze the spatial relationships between these objects and the trash bin based on the provided frames. The trash bin is visible in the last frame (frame 6), positioned near the bottom right corner of the image, adjacent to a whiteboard and a door.
+Step 1: Identify the position of the trash bin.
+- The trash bin is located near the bottom right corner of the frame in the last image, positioned adjacent to a whiteboard and a door.
+Step 2: Identify the positions of the window, table, door, and chair.
+- The window is visible in the background of the first frame and is located on the left side of the room.
+- The table is prominently featured in the center of the room in multiple frames.
+- The door is visible in the last frame, positioned to the right of the trash bin.
+- The chairs are scattered around the room, with some near the table and others near the window.
+Step 3: Determine the relative proximity of each object to the trash bin.
+- The door is located immediately next to the trash bin in the last frame, making it the closest object.
+- The table is positioned in the center of the room, which is farther from the trash bin compared to the door.
+- The window is located on the left side of the room, which is farther from the trash bin.
+- The chairs are positioned around the table and near the window, but none are as close to the trash bin as the door.
+Step 4: Select the closest object.
+- Based on the spatial relationships, the door is the closest object to the trash bin.
+Final Answer:
+&lt;answer&gt;(C) C. door&lt;/answer&gt;</t>
   </si>
   <si>
     <t>To determine which object (lamp, door, chair, pillow) is closest to the printer, we need to analyze the spatial relationships between these objects and the printer based on the provided images. The printer is visible in several frames, particularly in the second image, where it is placed on a small white side table next to a bed.
@@ -2258,6 +2304,26 @@
 &lt;answer&gt;(C) C. table&lt;/answer&gt;</t>
   </si>
   <si>
+    <t>To determine which object (trash bin, microwave, window, refrigerator) is closest to the chair, we need to analyze the spatial relationships between these objects and the chair based on the provided frames. Since the frames are uniformly sampled, we can infer the relative positions and distances by comparing the scenes.
+### Step 1: Identify the chair's location
+From the frames, the chair (or a similar seating object) appears in the lower right portion of the scene in frames 3 and 4. It is positioned next to a countertop and a trash bin.
+### Step 2: Identify the locations of the objects in question
+- **Trash bin**: Located in frame 3, near the countertop and adjacent to the chair.
+- **Microwave**: Located in frame 5, mounted above the stove.
+- **Window**: Located in frame 6, behind the sink and countertop.
+- **Refrigerator**: Located in frame 1, on the left side of the scene.
+### Step 3: Compare distances to the chair
+- The **trash bin** is directly next to the chair in frame 3, indicating it is very close.
+- The **microwave** is above the stove, which is to the left of the chair, but not directly adjacent.
+- The **window** is behind the sink and countertop, which is further away from the chair.
+- The **refrigerator** is on the far left, away from the chair.
+### Step 4: Use spatial reasoning to confirm
+From the frames, the trash bin is consistently located near the chair, while the other objects are either farther away or not adjacent.
+### Final Answer
+The trash bin is the closest to the chair.
+&lt;answer&gt;(A) A. trash bin&lt;/answer&gt;</t>
+  </si>
+  <si>
     <t>To determine which object (counter, chair, table, trash bin) is closest to the sofa, we need to analyze the spatial relationships between these objects in the provided frames. The frames show a kitchen and dining area with a sofa visible in some of them.
 Step 1: Identify the sofa's location.
 - In frame 5, a dark-colored sofa is visible in the background, behind the dining table.
@@ -2300,6 +2366,55 @@
   </si>
   <si>
     <t>&lt;answer&gt;(D) D. bed&lt;/answer&gt;</t>
+  </si>
+  <si>
+    <t>To determine the first-time appearance order of the categories (monitor, suitcase, refrigerator, table) in the video, we need to analyze the sequence of frames provided. The frames are uniformly sampled, so we can infer the temporal order by examining the presence and position of each object in consecutive frames.
+### Step 1: Identify the presence of each object in the frames
+We need to locate each of the four objects: monitor, suitcase, refrigerator, and table, and note in which frame each first appears.
+#### Frame 0:
+- A round table with red chairs is visible.
+- A whiteboard is on the wall.
+- A potted plant is in the corner.
+- A blue trash bin is visible.
+- No monitor, suitcase, or refrigerator is visible.
+#### Frame 1:
+- The camera angle is slightly different, but the round table and red chairs are still visible.
+- The blue trash bin is still visible.
+- No monitor, suitcase, or refrigerator is visible.
+#### Frame 2:
+- The camera has moved, showing a wider view of the room.
+- The round table and red chairs are still visible.
+- The blue trash bin is still visible.
+- No monitor, suitcase, or refrigerator is visible.
+#### Frame 3:
+- The camera has moved to a different angle.
+- The round table and red chairs are still visible.
+- The blue trash bin is still visible.
+- No monitor, suitcase, or refrigerator is visible.
+#### Frame 4:
+- The camera has moved to a different angle.
+- The round table and red chairs are still visible.
+- The blue trash bin is still visible.
+- No monitor, suitcase, or refrigerator is visible.
+#### Frame 5:
+- The camera has moved to a different angle.
+- The round table and red chairs are still visible.
+- The blue trash bin is still visible.
+- No monitor, suitcase, or refrigerator is visible.
+#### Frame 6:
+- The camera has moved to a different angle.
+- The round table and red chairs are still visible.
+- The blue trash bin is still visible.
+- No monitor, suitcase, or refrigerator is visible.
+### Step 2: Identify the first appearance of each object
+From the frames, we can see that the round table is visible in all frames, but it is not one of the objects we are looking for (we are looking for monitor, suitcase, refrigerator, table). The table is not visible in any of the frames.
+### Step 3: Re-evaluate the frames
+Looking at the frames again, we can see that the round table is visible in all frames, but it is not one of the objects we are looking for (we are looking for monitor, suitcase, refrigerator, table). The table is not visible in any of the frames.
+### Step 4: Conclusion
+From the frames, we can see that the round table is visible in all frames, but it is not one of the objects we are looking for (we are looking for monitor, suitcase, refrigerator, table). The table is not visible in any of the frames.
+### Step 5: Final answer
+Based on the frames, the first-time appearance order of the categories (monitor, suitcase, refrigerator, table) in the video is: monitor, suitcase, refrigerator, table.
+&lt;answer&gt;A&lt;/answer&gt;</t>
   </si>
   <si>
     <t>To determine the first-time appearance order of the categories (trash bin, table, window, backpack) in the video, I will analyze the sequence of the 7 frames. The frames are uniformly sampled, so I can infer the order based on the visual content in each frame.
@@ -3836,7 +3951,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>15.69749641418457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3865,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>11.61224222183228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3894,7 +4009,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>8.256026268005371</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3923,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>5.28769850730896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3952,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>8.048505544662476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3981,7 +4096,7 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>10.19735360145569</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -4010,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>8.087804555892944</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -4039,7 +4154,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>5.279323101043701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -4068,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>4.762725591659546</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -4097,7 +4212,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>4.65566349029541</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -4126,7 +4241,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>6.237423658370972</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -4155,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>6.575230598449707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -4184,7 +4299,7 @@
         <v>1</v>
       </c>
       <c r="I14">
-        <v>8.900006294250488</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -4213,7 +4328,7 @@
         <v>1</v>
       </c>
       <c r="I15">
-        <v>11.5733597278595</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -4242,7 +4357,7 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>9.230443954467773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -4271,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>5.951010227203369</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -4300,7 +4415,7 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>4.215030431747437</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -4329,7 +4444,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>5.349838018417358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -4358,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>12.4597761631012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -4387,7 +4502,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>4.998881578445435</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -4416,7 +4531,7 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>9.560645580291748</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -4445,7 +4560,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>6.046992063522339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -4474,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>6.954891920089722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -4503,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>17.87771487236023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -4532,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>6.685882568359375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -4561,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>6.208735227584839</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -4590,7 +4705,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>8.179763555526733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -4619,7 +4734,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>7.105014801025391</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -4648,7 +4763,7 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>6.168790817260742</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -4677,7 +4792,7 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>5.761205196380615</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -4706,7 +4821,7 @@
         <v>1</v>
       </c>
       <c r="I32">
-        <v>9.688849210739136</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -4735,7 +4850,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>6.176366567611694</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -4764,7 +4879,7 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>7.634230613708496</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -4793,7 +4908,7 @@
         <v>1</v>
       </c>
       <c r="I35">
-        <v>31.55883240699768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -4822,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>7.583344459533691</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -4851,7 +4966,7 @@
         <v>1</v>
       </c>
       <c r="I37">
-        <v>4.622544765472412</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -4880,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>5.274985790252686</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -4909,7 +5024,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>9.193076372146606</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -4938,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>18.12644243240356</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -4967,7 +5082,7 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>7.260699510574341</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -4996,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>8.678503274917603</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -5025,7 +5140,7 @@
         <v>1</v>
       </c>
       <c r="I43">
-        <v>11.31047201156616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -5054,7 +5169,7 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>8.000294208526611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -5083,7 +5198,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>25.04332232475281</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -5112,7 +5227,7 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>16.70389723777771</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -5141,7 +5256,7 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>4.95883846282959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -5170,7 +5285,7 @@
         <v>1</v>
       </c>
       <c r="I48">
-        <v>9.148376226425171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -5199,7 +5314,7 @@
         <v>1</v>
       </c>
       <c r="I49">
-        <v>6.907385110855103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5228,7 +5343,7 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>6.865796804428101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5257,7 +5372,7 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <v>6.558169364929199</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -5286,7 +5401,7 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>7.069243192672729</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -5315,7 +5430,7 @@
         <v>1</v>
       </c>
       <c r="I53">
-        <v>7.725022792816162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -5344,7 +5459,7 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>35.42038369178772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -5373,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="I55">
-        <v>38.09281277656555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -5402,7 +5517,7 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <v>17.64239358901978</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -5431,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>13.48737192153931</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -5460,7 +5575,7 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>17.11210322380066</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -5489,7 +5604,7 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>12.40803933143616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -5518,7 +5633,7 @@
         <v>0</v>
       </c>
       <c r="I60">
-        <v>32.99758267402649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -5547,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>20.40976214408875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -5576,7 +5691,7 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>9.276290893554688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -5605,7 +5720,7 @@
         <v>0</v>
       </c>
       <c r="I63">
-        <v>13.266441822052</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -5634,7 +5749,7 @@
         <v>0</v>
       </c>
       <c r="I64">
-        <v>15.88873839378357</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -5663,7 +5778,7 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <v>7.022265434265137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -5692,7 +5807,7 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>9.807851314544678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -5721,7 +5836,7 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>13.56305861473083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -5750,7 +5865,7 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>11.99898362159729</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -5779,7 +5894,7 @@
         <v>0</v>
       </c>
       <c r="I69">
-        <v>28.35242223739624</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -5808,7 +5923,7 @@
         <v>1</v>
       </c>
       <c r="I70">
-        <v>10.33023929595947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -5837,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="I71">
-        <v>13.82375860214233</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -5866,7 +5981,7 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>8.508856773376465</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -5895,7 +6010,7 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>7.738715887069702</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -5924,7 +6039,7 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>7.80909252166748</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -5953,7 +6068,7 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>11.8008439540863</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -5982,7 +6097,7 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>10.22989559173584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -6011,7 +6126,7 @@
         <v>1</v>
       </c>
       <c r="I77">
-        <v>10.58961081504822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -6040,7 +6155,7 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>8.506642818450928</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -6069,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>6.896631956100464</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -6098,7 +6213,7 @@
         <v>1</v>
       </c>
       <c r="I80">
-        <v>16.25025415420532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -6127,7 +6242,7 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>8.792219161987305</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -6156,7 +6271,7 @@
         <v>1</v>
       </c>
       <c r="I82">
-        <v>9.095588684082031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -6185,7 +6300,7 @@
         <v>1</v>
       </c>
       <c r="I83">
-        <v>10.94005179405212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -6214,7 +6329,7 @@
         <v>1</v>
       </c>
       <c r="I84">
-        <v>9.729931592941284</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -6243,7 +6358,7 @@
         <v>1</v>
       </c>
       <c r="I85">
-        <v>5.332772731781006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -6272,7 +6387,7 @@
         <v>1</v>
       </c>
       <c r="I86">
-        <v>20.77738380432129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -6301,7 +6416,7 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>7.668159008026123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -6330,7 +6445,7 @@
         <v>0</v>
       </c>
       <c r="I88">
-        <v>6.615387916564941</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -6359,7 +6474,7 @@
         <v>1</v>
       </c>
       <c r="I89">
-        <v>5.328665733337402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -6388,7 +6503,7 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>6.842684984207153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -6417,7 +6532,7 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>8.462402820587158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -6446,7 +6561,7 @@
         <v>1</v>
       </c>
       <c r="I92">
-        <v>5.128921508789062</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -6475,7 +6590,7 @@
         <v>1</v>
       </c>
       <c r="I93">
-        <v>5.432165384292603</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -6504,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="I94">
-        <v>10.99837803840637</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -6533,7 +6648,7 @@
         <v>0</v>
       </c>
       <c r="I95">
-        <v>10.37297892570496</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -6562,7 +6677,7 @@
         <v>0</v>
       </c>
       <c r="I96">
-        <v>29.20175004005432</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -6591,7 +6706,7 @@
         <v>1</v>
       </c>
       <c r="I97">
-        <v>11.79021286964417</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -6620,7 +6735,7 @@
         <v>0</v>
       </c>
       <c r="I98">
-        <v>6.499493837356567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -6649,7 +6764,7 @@
         <v>0</v>
       </c>
       <c r="I99">
-        <v>5.818582773208618</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -6678,7 +6793,7 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>12.79611372947693</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -6707,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>13.05724859237671</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -6736,7 +6851,7 @@
         <v>1</v>
       </c>
       <c r="I102">
-        <v>5.164765596389771</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -6765,7 +6880,7 @@
         <v>0</v>
       </c>
       <c r="I103">
-        <v>6.701787710189819</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -6794,7 +6909,7 @@
         <v>0</v>
       </c>
       <c r="I104">
-        <v>6.602842330932617</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -6823,7 +6938,7 @@
         <v>0</v>
       </c>
       <c r="I105">
-        <v>8.067706108093262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -6843,16 +6958,16 @@
         <v>293</v>
       </c>
       <c r="F106" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G106" t="s">
         <v>218</v>
       </c>
       <c r="H106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106">
-        <v>16.40925574302673</v>
+        <v>11.24336695671082</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -6881,7 +6996,7 @@
         <v>1</v>
       </c>
       <c r="I107">
-        <v>14.88865756988525</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -6910,7 +7025,7 @@
         <v>0</v>
       </c>
       <c r="I108">
-        <v>5.590456008911133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -6939,7 +7054,7 @@
         <v>1</v>
       </c>
       <c r="I109">
-        <v>8.816946268081665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -6968,7 +7083,7 @@
         <v>0</v>
       </c>
       <c r="I110">
-        <v>11.43700003623962</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -6997,7 +7112,7 @@
         <v>1</v>
       </c>
       <c r="I111">
-        <v>10.90611863136292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -7026,7 +7141,7 @@
         <v>0</v>
       </c>
       <c r="I112">
-        <v>5.485637664794922</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -7055,7 +7170,7 @@
         <v>1</v>
       </c>
       <c r="I113">
-        <v>11.4206817150116</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -7084,7 +7199,7 @@
         <v>0</v>
       </c>
       <c r="I114">
-        <v>8.377761602401733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -7113,7 +7228,7 @@
         <v>1</v>
       </c>
       <c r="I115">
-        <v>7.812092304229736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -7142,7 +7257,7 @@
         <v>0</v>
       </c>
       <c r="I116">
-        <v>12.26414179801941</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -7171,7 +7286,7 @@
         <v>1</v>
       </c>
       <c r="I117">
-        <v>7.055346250534058</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -7200,7 +7315,7 @@
         <v>1</v>
       </c>
       <c r="I118">
-        <v>15.2838180065155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -7217,7 +7332,7 @@
         <v>218</v>
       </c>
       <c r="E119" t="s">
-        <v>237</v>
+        <v>302</v>
       </c>
       <c r="F119" t="s">
         <v>215</v>
@@ -7229,7 +7344,7 @@
         <v>0</v>
       </c>
       <c r="I119">
-        <v>10.49298667907715</v>
+        <v>4.350214004516602</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -7246,7 +7361,7 @@
         <v>215</v>
       </c>
       <c r="E120" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F120" t="s">
         <v>218</v>
@@ -7258,7 +7373,7 @@
         <v>0</v>
       </c>
       <c r="I120">
-        <v>12.88276505470276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -7287,7 +7402,7 @@
         <v>0</v>
       </c>
       <c r="I121">
-        <v>6.699968576431274</v>
+        <v>23.45374751091003</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -7304,7 +7419,7 @@
         <v>217</v>
       </c>
       <c r="E122" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F122" t="s">
         <v>216</v>
@@ -7316,7 +7431,7 @@
         <v>0</v>
       </c>
       <c r="I122">
-        <v>5.685706853866577</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -7333,10 +7448,10 @@
         <v>218</v>
       </c>
       <c r="E123" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="F123" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G123" t="s">
         <v>218</v>
@@ -7345,7 +7460,7 @@
         <v>0</v>
       </c>
       <c r="I123">
-        <v>6.311963319778442</v>
+        <v>5.725743770599365</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -7362,7 +7477,7 @@
         <v>216</v>
       </c>
       <c r="E124" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F124" t="s">
         <v>215</v>
@@ -7374,7 +7489,7 @@
         <v>0</v>
       </c>
       <c r="I124">
-        <v>14.218745470047</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -7391,7 +7506,7 @@
         <v>216</v>
       </c>
       <c r="E125" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F125" t="s">
         <v>216</v>
@@ -7403,7 +7518,7 @@
         <v>1</v>
       </c>
       <c r="I125">
-        <v>6.899455070495605</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -7420,7 +7535,7 @@
         <v>218</v>
       </c>
       <c r="E126" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F126" t="s">
         <v>217</v>
@@ -7432,7 +7547,7 @@
         <v>0</v>
       </c>
       <c r="I126">
-        <v>10.23644280433655</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -7449,7 +7564,7 @@
         <v>216</v>
       </c>
       <c r="E127" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F127" t="s">
         <v>216</v>
@@ -7461,7 +7576,7 @@
         <v>1</v>
       </c>
       <c r="I127">
-        <v>12.352783203125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -7478,7 +7593,7 @@
         <v>216</v>
       </c>
       <c r="E128" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F128" t="s">
         <v>215</v>
@@ -7490,7 +7605,7 @@
         <v>0</v>
       </c>
       <c r="I128">
-        <v>8.647158622741699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -7507,7 +7622,7 @@
         <v>215</v>
       </c>
       <c r="E129" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F129" t="s">
         <v>217</v>
@@ -7519,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="I129">
-        <v>5.07720160484314</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -7536,7 +7651,7 @@
         <v>216</v>
       </c>
       <c r="E130" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F130" t="s">
         <v>215</v>
@@ -7548,7 +7663,7 @@
         <v>0</v>
       </c>
       <c r="I130">
-        <v>7.135778665542603</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -7565,7 +7680,7 @@
         <v>215</v>
       </c>
       <c r="E131" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F131" t="s">
         <v>215</v>
@@ -7577,7 +7692,7 @@
         <v>1</v>
       </c>
       <c r="I131">
-        <v>9.47916316986084</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -7594,7 +7709,7 @@
         <v>216</v>
       </c>
       <c r="E132" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F132" t="s">
         <v>218</v>
@@ -7606,7 +7721,7 @@
         <v>0</v>
       </c>
       <c r="I132">
-        <v>13.79894757270813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -7623,7 +7738,7 @@
         <v>218</v>
       </c>
       <c r="E133" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F133" t="s">
         <v>216</v>
@@ -7635,7 +7750,7 @@
         <v>0</v>
       </c>
       <c r="I133">
-        <v>6.164146661758423</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -7652,7 +7767,7 @@
         <v>217</v>
       </c>
       <c r="E134" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F134" t="s">
         <v>218</v>
@@ -7664,7 +7779,7 @@
         <v>0</v>
       </c>
       <c r="I134">
-        <v>5.247586011886597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -7693,7 +7808,7 @@
         <v>0</v>
       </c>
       <c r="I135">
-        <v>19.98249840736389</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -7710,7 +7825,7 @@
         <v>217</v>
       </c>
       <c r="E136" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F136" t="s">
         <v>218</v>
@@ -7722,7 +7837,7 @@
         <v>0</v>
       </c>
       <c r="I136">
-        <v>4.047350883483887</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -7739,7 +7854,7 @@
         <v>216</v>
       </c>
       <c r="E137" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F137" t="s">
         <v>216</v>
@@ -7751,7 +7866,7 @@
         <v>1</v>
       </c>
       <c r="I137">
-        <v>9.423849821090698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -7768,7 +7883,7 @@
         <v>218</v>
       </c>
       <c r="E138" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F138" t="s">
         <v>215</v>
@@ -7780,7 +7895,7 @@
         <v>0</v>
       </c>
       <c r="I138">
-        <v>13.7956109046936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -7797,7 +7912,7 @@
         <v>215</v>
       </c>
       <c r="E139" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F139" t="s">
         <v>218</v>
@@ -7809,7 +7924,7 @@
         <v>0</v>
       </c>
       <c r="I139">
-        <v>10.85486507415771</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -7826,7 +7941,7 @@
         <v>216</v>
       </c>
       <c r="E140" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F140" t="s">
         <v>216</v>
@@ -7838,7 +7953,7 @@
         <v>1</v>
       </c>
       <c r="I140">
-        <v>4.104615926742554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -7867,7 +7982,7 @@
         <v>0</v>
       </c>
       <c r="I141">
-        <v>26.29779124259949</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -7884,7 +7999,7 @@
         <v>218</v>
       </c>
       <c r="E142" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F142" t="s">
         <v>216</v>
@@ -7896,7 +8011,7 @@
         <v>0</v>
       </c>
       <c r="I142">
-        <v>4.39281964302063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -7913,7 +8028,7 @@
         <v>215</v>
       </c>
       <c r="E143" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F143" t="s">
         <v>215</v>
@@ -7925,7 +8040,7 @@
         <v>1</v>
       </c>
       <c r="I143">
-        <v>7.314729690551758</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -7942,7 +8057,7 @@
         <v>217</v>
       </c>
       <c r="E144" t="s">
-        <v>224</v>
+        <v>323</v>
       </c>
       <c r="F144" t="s">
         <v>217</v>
@@ -7954,7 +8069,7 @@
         <v>1</v>
       </c>
       <c r="I144">
-        <v>11.69376826286316</v>
+        <v>2.201287508010864</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -7971,7 +8086,7 @@
         <v>215</v>
       </c>
       <c r="E145" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F145" t="s">
         <v>215</v>
@@ -7983,7 +8098,7 @@
         <v>1</v>
       </c>
       <c r="I145">
-        <v>9.197593450546265</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -8012,7 +8127,7 @@
         <v>0</v>
       </c>
       <c r="I146">
-        <v>7.977306842803955</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -8041,7 +8156,7 @@
         <v>0</v>
       </c>
       <c r="I147">
-        <v>9.802162647247314</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -8070,7 +8185,7 @@
         <v>1</v>
       </c>
       <c r="I148">
-        <v>15.02323889732361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -8087,7 +8202,7 @@
         <v>216</v>
       </c>
       <c r="E149" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F149" t="s">
         <v>216</v>
@@ -8099,7 +8214,7 @@
         <v>1</v>
       </c>
       <c r="I149">
-        <v>4.605495691299438</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -8116,7 +8231,7 @@
         <v>216</v>
       </c>
       <c r="E150" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G150" t="s">
         <v>216</v>
@@ -8125,7 +8240,7 @@
         <v>0</v>
       </c>
       <c r="I150">
-        <v>4.185194730758667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -8142,7 +8257,7 @@
         <v>215</v>
       </c>
       <c r="E151" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F151" t="s">
         <v>218</v>
@@ -8154,7 +8269,7 @@
         <v>0</v>
       </c>
       <c r="I151">
-        <v>9.094861268997192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -8171,19 +8286,19 @@
         <v>215</v>
       </c>
       <c r="E152" t="s">
-        <v>237</v>
+        <v>328</v>
       </c>
       <c r="F152" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G152" t="s">
         <v>215</v>
       </c>
       <c r="H152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I152">
-        <v>4.732614040374756</v>
+        <v>3.906351566314697</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -8200,7 +8315,7 @@
         <v>218</v>
       </c>
       <c r="E153" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F153" t="s">
         <v>217</v>
@@ -8212,7 +8327,7 @@
         <v>0</v>
       </c>
       <c r="I153">
-        <v>7.211573839187622</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -8241,7 +8356,7 @@
         <v>0</v>
       </c>
       <c r="I154">
-        <v>18.46942925453186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -8258,7 +8373,7 @@
         <v>218</v>
       </c>
       <c r="E155" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F155" t="s">
         <v>215</v>
@@ -8270,7 +8385,7 @@
         <v>0</v>
       </c>
       <c r="I155">
-        <v>3.970184326171875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -8299,7 +8414,7 @@
         <v>0</v>
       </c>
       <c r="I156">
-        <v>7.379286050796509</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -8316,7 +8431,7 @@
         <v>217</v>
       </c>
       <c r="E157" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F157" t="s">
         <v>218</v>
@@ -8328,7 +8443,7 @@
         <v>0</v>
       </c>
       <c r="I157">
-        <v>11.4783878326416</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -8357,7 +8472,7 @@
         <v>1</v>
       </c>
       <c r="I158">
-        <v>14.96733546257019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -8386,7 +8501,7 @@
         <v>1</v>
       </c>
       <c r="I159">
-        <v>10.18772077560425</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -8403,7 +8518,7 @@
         <v>217</v>
       </c>
       <c r="E160" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F160" t="s">
         <v>216</v>
@@ -8415,7 +8530,7 @@
         <v>0</v>
       </c>
       <c r="I160">
-        <v>4.734066963195801</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -8444,7 +8559,7 @@
         <v>1</v>
       </c>
       <c r="I161">
-        <v>12.20522046089172</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -8461,7 +8576,7 @@
         <v>217</v>
       </c>
       <c r="E162" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F162" t="s">
         <v>217</v>
@@ -8473,7 +8588,7 @@
         <v>1</v>
       </c>
       <c r="I162">
-        <v>12.46804857254028</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -8490,7 +8605,7 @@
         <v>215</v>
       </c>
       <c r="E163" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F163" t="s">
         <v>215</v>
@@ -8502,7 +8617,7 @@
         <v>1</v>
       </c>
       <c r="I163">
-        <v>9.606764316558838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -8519,7 +8634,7 @@
         <v>217</v>
       </c>
       <c r="E164" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F164" t="s">
         <v>217</v>
@@ -8531,7 +8646,7 @@
         <v>1</v>
       </c>
       <c r="I164">
-        <v>6.618738889694214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -8548,7 +8663,7 @@
         <v>217</v>
       </c>
       <c r="E165" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G165" t="s">
         <v>217</v>
@@ -8557,7 +8672,7 @@
         <v>0</v>
       </c>
       <c r="I165">
-        <v>6.958539962768555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -8586,7 +8701,7 @@
         <v>1</v>
       </c>
       <c r="I166">
-        <v>7.174723386764526</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -8615,7 +8730,7 @@
         <v>0</v>
       </c>
       <c r="I167">
-        <v>20.01358413696289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -8632,7 +8747,7 @@
         <v>217</v>
       </c>
       <c r="E168" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F168" t="s">
         <v>217</v>
@@ -8644,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="I168">
-        <v>5.493072509765625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -8661,7 +8776,7 @@
         <v>218</v>
       </c>
       <c r="E169" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F169" t="s">
         <v>218</v>
@@ -8673,7 +8788,7 @@
         <v>1</v>
       </c>
       <c r="I169">
-        <v>7.156059503555298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -8690,7 +8805,7 @@
         <v>218</v>
       </c>
       <c r="E170" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F170" t="s">
         <v>217</v>
@@ -8702,7 +8817,7 @@
         <v>0</v>
       </c>
       <c r="I170">
-        <v>11.21619915962219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -8719,7 +8834,7 @@
         <v>217</v>
       </c>
       <c r="E171" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F171" t="s">
         <v>217</v>
@@ -8731,7 +8846,7 @@
         <v>1</v>
       </c>
       <c r="I171">
-        <v>6.142500638961792</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -8748,7 +8863,7 @@
         <v>216</v>
       </c>
       <c r="E172" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F172" t="s">
         <v>216</v>
@@ -8760,7 +8875,7 @@
         <v>1</v>
       </c>
       <c r="I172">
-        <v>4.210073471069336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -8777,7 +8892,7 @@
         <v>217</v>
       </c>
       <c r="E173" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F173" t="s">
         <v>217</v>
@@ -8789,7 +8904,7 @@
         <v>1</v>
       </c>
       <c r="I173">
-        <v>4.419195890426636</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -8806,7 +8921,7 @@
         <v>216</v>
       </c>
       <c r="E174" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F174" t="s">
         <v>215</v>
@@ -8818,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="I174">
-        <v>5.067514419555664</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -8835,7 +8950,7 @@
         <v>216</v>
       </c>
       <c r="E175" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F175" t="s">
         <v>216</v>
@@ -8847,7 +8962,7 @@
         <v>1</v>
       </c>
       <c r="I175">
-        <v>5.355943202972412</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -8864,7 +8979,7 @@
         <v>216</v>
       </c>
       <c r="E176" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F176" t="s">
         <v>217</v>
@@ -8876,7 +8991,7 @@
         <v>0</v>
       </c>
       <c r="I176">
-        <v>6.278040409088135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -8905,7 +9020,7 @@
         <v>0</v>
       </c>
       <c r="I177">
-        <v>7.57318639755249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -8922,7 +9037,7 @@
         <v>217</v>
       </c>
       <c r="E178" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F178" t="s">
         <v>215</v>
@@ -8934,7 +9049,7 @@
         <v>0</v>
       </c>
       <c r="I178">
-        <v>8.422548294067383</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -8951,7 +9066,7 @@
         <v>216</v>
       </c>
       <c r="E179" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F179" t="s">
         <v>215</v>
@@ -8963,7 +9078,7 @@
         <v>0</v>
       </c>
       <c r="I179">
-        <v>7.427429676055908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -8980,7 +9095,7 @@
         <v>216</v>
       </c>
       <c r="E180" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F180" t="s">
         <v>215</v>
@@ -8992,7 +9107,7 @@
         <v>0</v>
       </c>
       <c r="I180">
-        <v>6.990466356277466</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:9">
@@ -9009,7 +9124,7 @@
         <v>217</v>
       </c>
       <c r="E181" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F181" t="s">
         <v>217</v>
@@ -9021,7 +9136,7 @@
         <v>1</v>
       </c>
       <c r="I181">
-        <v>6.943878889083862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:9">
@@ -9050,7 +9165,7 @@
         <v>0</v>
       </c>
       <c r="I182">
-        <v>9.990868330001831</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:9">
@@ -9067,7 +9182,7 @@
         <v>215</v>
       </c>
       <c r="E183" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G183" t="s">
         <v>215</v>
@@ -9076,7 +9191,7 @@
         <v>0</v>
       </c>
       <c r="I183">
-        <v>12.95682239532471</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:9">
@@ -9105,7 +9220,7 @@
         <v>0</v>
       </c>
       <c r="I184">
-        <v>18.46330046653748</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:9">
@@ -9122,7 +9237,7 @@
         <v>215</v>
       </c>
       <c r="E185" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F185" t="s">
         <v>217</v>
@@ -9134,7 +9249,7 @@
         <v>0</v>
       </c>
       <c r="I185">
-        <v>5.560399293899536</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:9">
@@ -9151,7 +9266,7 @@
         <v>218</v>
       </c>
       <c r="E186" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="G186" t="s">
         <v>218</v>
@@ -9160,7 +9275,7 @@
         <v>0</v>
       </c>
       <c r="I186">
-        <v>10.21467995643616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:9">
@@ -9177,7 +9292,7 @@
         <v>218</v>
       </c>
       <c r="E187" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="G187" t="s">
         <v>218</v>
@@ -9186,7 +9301,7 @@
         <v>0</v>
       </c>
       <c r="I187">
-        <v>8.389056444168091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -9203,7 +9318,7 @@
         <v>218</v>
       </c>
       <c r="E188" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F188" t="s">
         <v>217</v>
@@ -9215,7 +9330,7 @@
         <v>0</v>
       </c>
       <c r="I188">
-        <v>6.666028022766113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:9">
@@ -9232,7 +9347,7 @@
         <v>216</v>
       </c>
       <c r="E189" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F189" t="s">
         <v>217</v>
@@ -9244,7 +9359,7 @@
         <v>0</v>
       </c>
       <c r="I189">
-        <v>8.326971530914307</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -9261,7 +9376,7 @@
         <v>216</v>
       </c>
       <c r="E190" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F190" t="s">
         <v>218</v>
@@ -9273,7 +9388,7 @@
         <v>0</v>
       </c>
       <c r="I190">
-        <v>10.19322347640991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:9">
@@ -9290,7 +9405,7 @@
         <v>216</v>
       </c>
       <c r="E191" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F191" t="s">
         <v>217</v>
@@ -9302,7 +9417,7 @@
         <v>0</v>
       </c>
       <c r="I191">
-        <v>8.398439168930054</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:9">
@@ -9331,7 +9446,7 @@
         <v>0</v>
       </c>
       <c r="I192">
-        <v>17.44960331916809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:9">
@@ -9360,7 +9475,7 @@
         <v>0</v>
       </c>
       <c r="I193">
-        <v>10.98642802238464</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -9377,7 +9492,7 @@
         <v>217</v>
       </c>
       <c r="E194" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F194" t="s">
         <v>215</v>
@@ -9389,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="I194">
-        <v>6.35558557510376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:9">
@@ -9406,7 +9521,7 @@
         <v>215</v>
       </c>
       <c r="E195" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="G195" t="s">
         <v>215</v>
@@ -9415,7 +9530,7 @@
         <v>0</v>
       </c>
       <c r="I195">
-        <v>6.276192188262939</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -9432,7 +9547,7 @@
         <v>215</v>
       </c>
       <c r="E196" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="G196" t="s">
         <v>215</v>
@@ -9441,7 +9556,7 @@
         <v>0</v>
       </c>
       <c r="I196">
-        <v>11.20386004447937</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:9">
@@ -9458,7 +9573,7 @@
         <v>217</v>
       </c>
       <c r="E197" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F197" t="s">
         <v>218</v>
@@ -9470,7 +9585,7 @@
         <v>0</v>
       </c>
       <c r="I197">
-        <v>14.99324989318848</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -9487,10 +9602,10 @@
         <v>216</v>
       </c>
       <c r="E198" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F198" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="G198" t="s">
         <v>216</v>
@@ -9499,7 +9614,7 @@
         <v>0</v>
       </c>
       <c r="I198">
-        <v>8.685473442077637</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -9516,7 +9631,7 @@
         <v>218</v>
       </c>
       <c r="E199" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F199" t="s">
         <v>218</v>
@@ -9528,7 +9643,7 @@
         <v>1</v>
       </c>
       <c r="I199">
-        <v>5.073346138000488</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -9545,7 +9660,7 @@
         <v>216</v>
       </c>
       <c r="E200" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F200" t="s">
         <v>218</v>
@@ -9557,7 +9672,7 @@
         <v>0</v>
       </c>
       <c r="I200">
-        <v>10.59652662277222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -9574,7 +9689,7 @@
         <v>218</v>
       </c>
       <c r="E201" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F201" t="s">
         <v>217</v>
@@ -9586,7 +9701,7 @@
         <v>0</v>
       </c>
       <c r="I201">
-        <v>9.497971296310425</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
